--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -94,7 +94,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>copyright HL7 Japan (出典：HL7-0241)
+    <t>Copyright HL7 Japan (出典：HL7-0241)
 Copyright Japanese  Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
   </si>
   <si>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -95,7 +95,7 @@
   </si>
   <si>
     <t>Copyright HL7 Japan (出典：HL7-0241)
-Copyright Japanese  Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
+Copyright Japanese Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
